--- a/work/통합 문서1.xlsx
+++ b/work/통합 문서1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\seohabucks\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE12A8F-3CF2-4E22-9227-8D16367F3971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C54DC2-4A17-4C42-B604-7CD28E3AA614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{4A079E56-68E5-44B1-8071-E38A8DF1D34E}"/>
   </bookViews>
@@ -20,8 +20,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
-    <pivotCache cacheId="49" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -561,9 +561,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="182" formatCode="yy&quot;년&quot;\ m&quot;월&quot;;@"/>
-    <numFmt numFmtId="183" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="185" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
+    <numFmt numFmtId="176" formatCode="yy&quot;년&quot;\ m&quot;월&quot;;@"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="178" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -792,7 +792,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -802,103 +802,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -910,7 +901,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -922,7 +913,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -934,7 +925,7 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -942,268 +933,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="KoPub돋움체 Light"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="183" formatCode="0_);[Red]\(0\)"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="KoPub돋움체 Light"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="182" formatCode="yy&quot;년&quot;\ m&quot;월&quot;;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="KoPub돋움체 Light"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="185" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="KoPub돋움체 Light"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="KoPub돋움체 Light"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="KoPub돋움체 Medium"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="KoPub돋움체 Medium"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="KoPub돋움체 Medium"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1292,7 +1021,7 @@
         <charset val="129"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="185" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
+      <numFmt numFmtId="178" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1329,7 +1058,7 @@
         <charset val="129"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="183" formatCode="0_);[Red]\(0\)"/>
+      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1337,6 +1066,45 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="KoPub돋움체 Medium"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1393,13 +1161,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1414,6 +1175,243 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="KoPub돋움체 Medium"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="KoPub돋움체 Medium"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="KoPub돋움체 Light"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="KoPub돋움체 Light"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="yy&quot;년&quot;\ m&quot;월&quot;;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="KoPub돋움체 Light"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="KoPub돋움체 Light"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="KoPub돋움체 Light"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1442,13 +1440,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
       </border>
     </dxf>
   </dxfs>
@@ -1486,10 +1477,10 @@
         <s v="수도권(IV)광역상수도(시화안산계통)복선화사업 시설공사중 부단수 차단 공사"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="수량" numFmtId="183">
+    <cacheField name="수량" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
     </cacheField>
-    <cacheField name="시공년월" numFmtId="185">
+    <cacheField name="시공년월" numFmtId="178">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-12-24T00:00:00" maxDate="2026-06-25T00:00:00" count="9">
         <d v="2026-03-31T00:00:00"/>
         <d v="2023-12-24T00:00:00"/>
@@ -1623,7 +1614,7 @@
         <s v="수도권광역상수도(Ⅰ단계) 잠원동구간 관로 이설사업(2차)"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="선정일자" numFmtId="185">
+    <cacheField name="선정일자" numFmtId="178">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-03-06T00:00:00" maxDate="2026-05-23T00:00:00" count="45">
         <d v="2023-03-06T00:00:00"/>
         <d v="2023-03-08T00:00:00"/>
@@ -2383,7 +2374,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4D88A407-2A03-42A5-B8A2-675F849A360A}" name="피벗 테이블13" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4D88A407-2A03-42A5-B8A2-675F849A360A}" name="피벗 테이블13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
   <location ref="A3:C100" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" showAll="0">
@@ -2439,7 +2430,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" numFmtId="185" showAll="0">
+    <pivotField axis="axisRow" compact="0" numFmtId="178" showAll="0">
       <items count="46">
         <item x="0"/>
         <item x="1"/>
@@ -2877,7 +2868,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F33251-8B97-47ED-93D9-D59A1FB6A316}" name="피벗 테이블11" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F33251-8B97-47ED-93D9-D59A1FB6A316}" name="피벗 테이블11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0">
@@ -2933,7 +2924,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" numFmtId="185" showAll="0">
+    <pivotField axis="axisPage" numFmtId="178" showAll="0">
       <items count="46">
         <item x="0"/>
         <item x="1"/>
@@ -3073,7 +3064,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B236DD32-0033-4445-95CB-B69B8A67C787}" name="피벗 테이블1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B236DD32-0033-4445-95CB-B69B8A67C787}" name="피벗 테이블1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
@@ -3091,8 +3082,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="183" showAll="0"/>
-    <pivotField numFmtId="185" showAll="0">
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0">
       <items count="10">
         <item x="1"/>
         <item x="2"/>
@@ -3198,7 +3189,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="최대 : 관경" fld="0" subtotal="max" baseField="1" baseItem="0"/>
-    <dataField name="합계 : 수량" fld="2" baseField="0" baseItem="0" numFmtId="183"/>
+    <dataField name="합계 : 수량" fld="2" baseField="0" baseItem="0" numFmtId="177"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -3213,34 +3204,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F16DDA2B-0F1E-401E-8F8A-FDA2E2D1BA99}" name="시공선정실적" displayName="시공선정실적" ref="A1:D142" totalsRowShown="0" headerRowDxfId="16" dataDxfId="4" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F16DDA2B-0F1E-401E-8F8A-FDA2E2D1BA99}" name="시공선정실적" displayName="시공선정실적" ref="A1:D142" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:D142" xr:uid="{F16DDA2B-0F1E-401E-8F8A-FDA2E2D1BA99}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D83">
     <sortCondition ref="B1:B83"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="2" xr3:uid="{60C2A2CA-FF9C-482A-BD9B-1B7BD5603B88}" name="공사명" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{005F7590-3C2A-4F6D-94C8-860DE409DF88}" name="선정일자" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{CB1DB152-35D6-43D1-BFFD-A4B7415D426D}" name="발주기관명" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{FA843834-92E9-4718-9CF5-F06102603071}" name="관경" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{60C2A2CA-FF9C-482A-BD9B-1B7BD5603B88}" name="공사명" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{005F7590-3C2A-4F6D-94C8-860DE409DF88}" name="선정일자" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{CB1DB152-35D6-43D1-BFFD-A4B7415D426D}" name="발주기관명" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{FA843834-92E9-4718-9CF5-F06102603071}" name="관경" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{343B6AC1-4895-440B-87B0-41517F4E9198}" name="표2" displayName="표2" ref="A1:F16" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{343B6AC1-4895-440B-87B0-41517F4E9198}" name="표2" displayName="표2" ref="A1:F16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F16" xr:uid="{343B6AC1-4895-440B-87B0-41517F4E9198}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F16">
     <sortCondition descending="1" ref="F1:F16"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="4" xr3:uid="{79BB53FB-1B97-421C-9546-8D5FF3F6C46B}" name="관경" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{90410CDF-EF89-455E-8AEF-B3DAA6018D9F}" name="공사" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{A73756A1-4010-4546-9809-129445D7309C}" name="수량" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{F20E98FF-6730-4BC6-B6B1-D0D55F16BA32}" name="시공년월" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{D4D744FB-E62E-4696-98B2-3E4B33775BF5}" name="발주처" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{43B31222-1C61-42A0-8BEF-A15779F4BA0B}" name="도급사" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{79BB53FB-1B97-421C-9546-8D5FF3F6C46B}" name="관경" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{90410CDF-EF89-455E-8AEF-B3DAA6018D9F}" name="공사" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{A73756A1-4010-4546-9809-129445D7309C}" name="수량" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F20E98FF-6730-4BC6-B6B1-D0D55F16BA32}" name="시공년월" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{D4D744FB-E62E-4696-98B2-3E4B33775BF5}" name="발주처" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{43B31222-1C61-42A0-8BEF-A15779F4BA0B}" name="도급사" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3577,7 +3568,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>144</v>
       </c>
       <c r="B1" t="s">
@@ -3585,10 +3576,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -3599,7 +3590,7 @@
       <c r="A4" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
@@ -3607,7 +3598,7 @@
       <c r="B5" s="6">
         <v>45714</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5">
         <v>0</v>
       </c>
     </row>
@@ -3615,7 +3606,7 @@
       <c r="A6" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
@@ -3623,7 +3614,7 @@
       <c r="B7" s="6">
         <v>45498</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7">
         <v>0</v>
       </c>
     </row>
@@ -3631,7 +3622,7 @@
       <c r="A8" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8">
         <v>0</v>
       </c>
     </row>
@@ -3639,7 +3630,7 @@
       <c r="B9" s="6">
         <v>45492</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9">
         <v>0</v>
       </c>
     </row>
@@ -3647,7 +3638,7 @@
       <c r="A10" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10">
         <v>0</v>
       </c>
     </row>
@@ -3655,7 +3646,7 @@
       <c r="B11" s="6">
         <v>45461</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11">
         <v>0</v>
       </c>
     </row>
@@ -3663,7 +3654,7 @@
       <c r="A12" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12">
         <v>0</v>
       </c>
     </row>
@@ -3671,7 +3662,7 @@
       <c r="B13" s="6">
         <v>45464</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
@@ -3679,7 +3670,7 @@
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14">
         <v>0</v>
       </c>
     </row>
@@ -3687,7 +3678,7 @@
       <c r="B15" s="6">
         <v>45210</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15">
         <v>0</v>
       </c>
     </row>
@@ -3695,7 +3686,7 @@
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16">
         <v>0</v>
       </c>
     </row>
@@ -3703,7 +3694,7 @@
       <c r="B17" s="6">
         <v>45840</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17">
         <v>0</v>
       </c>
     </row>
@@ -3711,7 +3702,7 @@
       <c r="A18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18">
         <v>0</v>
       </c>
     </row>
@@ -3719,7 +3710,7 @@
       <c r="B19" s="6">
         <v>45029</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19">
         <v>0</v>
       </c>
     </row>
@@ -3727,7 +3718,7 @@
       <c r="B20" s="6">
         <v>45981</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20">
         <v>0</v>
       </c>
     </row>
@@ -3735,7 +3726,7 @@
       <c r="A21" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21">
         <v>0</v>
       </c>
     </row>
@@ -3743,7 +3734,7 @@
       <c r="B22" s="6">
         <v>45134</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22">
         <v>0</v>
       </c>
     </row>
@@ -3751,7 +3742,7 @@
       <c r="A23" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23">
         <v>0</v>
       </c>
     </row>
@@ -3759,7 +3750,7 @@
       <c r="B24" s="6">
         <v>46154</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24">
         <v>0</v>
       </c>
     </row>
@@ -3767,7 +3758,7 @@
       <c r="A25" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25">
         <v>0</v>
       </c>
     </row>
@@ -3775,7 +3766,7 @@
       <c r="B26" s="6">
         <v>44991</v>
       </c>
-      <c r="C26" s="33">
+      <c r="C26">
         <v>0</v>
       </c>
     </row>
@@ -3783,7 +3774,7 @@
       <c r="A27" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27">
         <v>0</v>
       </c>
     </row>
@@ -3791,7 +3782,7 @@
       <c r="B28" s="6">
         <v>45743</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28">
         <v>0</v>
       </c>
     </row>
@@ -3799,7 +3790,7 @@
       <c r="A29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29">
         <v>0</v>
       </c>
     </row>
@@ -3807,7 +3798,7 @@
       <c r="B30" s="6">
         <v>45044</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30">
         <v>0</v>
       </c>
     </row>
@@ -3815,7 +3806,7 @@
       <c r="A31" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31">
         <v>0</v>
       </c>
     </row>
@@ -3823,7 +3814,7 @@
       <c r="B32" s="6">
         <v>45177</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32">
         <v>0</v>
       </c>
     </row>
@@ -3831,7 +3822,7 @@
       <c r="A33" t="s">
         <v>132</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33">
         <v>0</v>
       </c>
     </row>
@@ -3839,7 +3830,7 @@
       <c r="B34" s="6">
         <v>45946</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34">
         <v>0</v>
       </c>
     </row>
@@ -3847,7 +3838,7 @@
       <c r="A35" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35">
         <v>0</v>
       </c>
     </row>
@@ -3855,7 +3846,7 @@
       <c r="B36" s="6">
         <v>45862</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36">
         <v>0</v>
       </c>
     </row>
@@ -3863,7 +3854,7 @@
       <c r="A37" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37">
         <v>0</v>
       </c>
     </row>
@@ -3871,7 +3862,7 @@
       <c r="B38" s="6">
         <v>45877</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38">
         <v>0</v>
       </c>
     </row>
@@ -3879,7 +3870,7 @@
       <c r="A39" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39">
         <v>0</v>
       </c>
     </row>
@@ -3887,7 +3878,7 @@
       <c r="B40" s="6">
         <v>45680</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40">
         <v>0</v>
       </c>
     </row>
@@ -3895,7 +3886,7 @@
       <c r="A41" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41">
         <v>0</v>
       </c>
     </row>
@@ -3903,7 +3894,7 @@
       <c r="B42" s="6">
         <v>45139</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42">
         <v>0</v>
       </c>
     </row>
@@ -3911,7 +3902,7 @@
       <c r="A43" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="33">
+      <c r="C43">
         <v>0</v>
       </c>
     </row>
@@ -3919,7 +3910,7 @@
       <c r="B44" s="6">
         <v>45975</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44">
         <v>0</v>
       </c>
     </row>
@@ -3927,7 +3918,7 @@
       <c r="A45" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45">
         <v>0</v>
       </c>
     </row>
@@ -3935,7 +3926,7 @@
       <c r="B46" s="6">
         <v>45882</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46">
         <v>0</v>
       </c>
     </row>
@@ -3943,7 +3934,7 @@
       <c r="A47" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47">
         <v>0</v>
       </c>
     </row>
@@ -3951,7 +3942,7 @@
       <c r="B48" s="6">
         <v>45006</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48">
         <v>0</v>
       </c>
     </row>
@@ -3959,7 +3950,7 @@
       <c r="A49" t="s">
         <v>136</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49">
         <v>0</v>
       </c>
     </row>
@@ -3967,7 +3958,7 @@
       <c r="B50" s="6">
         <v>44993</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50">
         <v>0</v>
       </c>
     </row>
@@ -3975,7 +3966,7 @@
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51">
         <v>0</v>
       </c>
     </row>
@@ -3983,7 +3974,7 @@
       <c r="B52" s="6">
         <v>45630</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52">
         <v>0</v>
       </c>
     </row>
@@ -3991,7 +3982,7 @@
       <c r="A53" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53">
         <v>0</v>
       </c>
     </row>
@@ -3999,7 +3990,7 @@
       <c r="B54" s="6">
         <v>45973</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54">
         <v>0</v>
       </c>
     </row>
@@ -4007,7 +3998,7 @@
       <c r="A55" t="s">
         <v>28</v>
       </c>
-      <c r="C55" s="33">
+      <c r="C55">
         <v>0</v>
       </c>
     </row>
@@ -4015,7 +4006,7 @@
       <c r="B56" s="6">
         <v>45975</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56">
         <v>0</v>
       </c>
     </row>
@@ -4023,7 +4014,7 @@
       <c r="A57" t="s">
         <v>26</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57">
         <v>0</v>
       </c>
     </row>
@@ -4031,7 +4022,7 @@
       <c r="B58" s="6">
         <v>45924</v>
       </c>
-      <c r="C58" s="33">
+      <c r="C58">
         <v>0</v>
       </c>
     </row>
@@ -4039,7 +4030,7 @@
       <c r="A59" t="s">
         <v>137</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59">
         <v>0</v>
       </c>
     </row>
@@ -4047,7 +4038,7 @@
       <c r="B60" s="6">
         <v>45270</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60">
         <v>0</v>
       </c>
     </row>
@@ -4055,7 +4046,7 @@
       <c r="A61" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="33">
+      <c r="C61">
         <v>0</v>
       </c>
     </row>
@@ -4063,7 +4054,7 @@
       <c r="B62" s="6">
         <v>45971</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62">
         <v>0</v>
       </c>
     </row>
@@ -4071,7 +4062,7 @@
       <c r="A63" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63">
         <v>0</v>
       </c>
     </row>
@@ -4079,7 +4070,7 @@
       <c r="B64" s="6">
         <v>46164</v>
       </c>
-      <c r="C64" s="33">
+      <c r="C64">
         <v>0</v>
       </c>
     </row>
@@ -4087,7 +4078,7 @@
       <c r="A65" t="s">
         <v>30</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65">
         <v>0</v>
       </c>
     </row>
@@ -4095,7 +4086,7 @@
       <c r="B66" s="6">
         <v>45996</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66">
         <v>0</v>
       </c>
     </row>
@@ -4103,7 +4094,7 @@
       <c r="A67" t="s">
         <v>24</v>
       </c>
-      <c r="C67" s="33">
+      <c r="C67">
         <v>0</v>
       </c>
     </row>
@@ -4111,7 +4102,7 @@
       <c r="B68" s="6">
         <v>45870</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68">
         <v>0</v>
       </c>
     </row>
@@ -4119,7 +4110,7 @@
       <c r="A69" t="s">
         <v>10</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69">
         <v>0</v>
       </c>
     </row>
@@ -4127,7 +4118,7 @@
       <c r="B70" s="6">
         <v>45762</v>
       </c>
-      <c r="C70" s="33">
+      <c r="C70">
         <v>0</v>
       </c>
     </row>
@@ -4135,7 +4126,7 @@
       <c r="A71" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71">
         <v>0</v>
       </c>
     </row>
@@ -4143,7 +4134,7 @@
       <c r="B72" s="6">
         <v>45175</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72">
         <v>0</v>
       </c>
     </row>
@@ -4151,7 +4142,7 @@
       <c r="A73" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="33">
+      <c r="C73">
         <v>0</v>
       </c>
     </row>
@@ -4159,7 +4150,7 @@
       <c r="B74" s="6">
         <v>46041</v>
       </c>
-      <c r="C74" s="33">
+      <c r="C74">
         <v>0</v>
       </c>
     </row>
@@ -4167,7 +4158,7 @@
       <c r="A75" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="33">
+      <c r="C75">
         <v>0</v>
       </c>
     </row>
@@ -4175,7 +4166,7 @@
       <c r="B76" s="6">
         <v>45797</v>
       </c>
-      <c r="C76" s="33">
+      <c r="C76">
         <v>0</v>
       </c>
     </row>
@@ -4183,7 +4174,7 @@
       <c r="A77" t="s">
         <v>140</v>
       </c>
-      <c r="C77" s="33">
+      <c r="C77">
         <v>0</v>
       </c>
     </row>
@@ -4191,7 +4182,7 @@
       <c r="B78" s="6">
         <v>45966</v>
       </c>
-      <c r="C78" s="33">
+      <c r="C78">
         <v>0</v>
       </c>
     </row>
@@ -4199,7 +4190,7 @@
       <c r="A79" t="s">
         <v>141</v>
       </c>
-      <c r="C79" s="33">
+      <c r="C79">
         <v>0</v>
       </c>
     </row>
@@ -4207,7 +4198,7 @@
       <c r="B80" s="6">
         <v>45966</v>
       </c>
-      <c r="C80" s="33">
+      <c r="C80">
         <v>0</v>
       </c>
     </row>
@@ -4215,7 +4206,7 @@
       <c r="A81" t="s">
         <v>142</v>
       </c>
-      <c r="C81" s="33">
+      <c r="C81">
         <v>0</v>
       </c>
     </row>
@@ -4223,7 +4214,7 @@
       <c r="B82" s="6">
         <v>45971</v>
       </c>
-      <c r="C82" s="33">
+      <c r="C82">
         <v>0</v>
       </c>
     </row>
@@ -4231,7 +4222,7 @@
       <c r="A83" t="s">
         <v>117</v>
       </c>
-      <c r="C83" s="33">
+      <c r="C83">
         <v>0</v>
       </c>
     </row>
@@ -4239,7 +4230,7 @@
       <c r="B84" s="6">
         <v>45958</v>
       </c>
-      <c r="C84" s="33">
+      <c r="C84">
         <v>0</v>
       </c>
     </row>
@@ -4247,7 +4238,7 @@
       <c r="A85" t="s">
         <v>119</v>
       </c>
-      <c r="C85" s="33">
+      <c r="C85">
         <v>0</v>
       </c>
     </row>
@@ -4255,7 +4246,7 @@
       <c r="B86" s="6">
         <v>45958</v>
       </c>
-      <c r="C86" s="33">
+      <c r="C86">
         <v>0</v>
       </c>
     </row>
@@ -4263,7 +4254,7 @@
       <c r="A87" t="s">
         <v>143</v>
       </c>
-      <c r="C87" s="33">
+      <c r="C87">
         <v>0</v>
       </c>
     </row>
@@ -4271,7 +4262,7 @@
       <c r="B88" s="6">
         <v>45100</v>
       </c>
-      <c r="C88" s="33">
+      <c r="C88">
         <v>0</v>
       </c>
     </row>
@@ -4279,7 +4270,7 @@
       <c r="A89" t="s">
         <v>21</v>
       </c>
-      <c r="C89" s="33">
+      <c r="C89">
         <v>0</v>
       </c>
     </row>
@@ -4287,7 +4278,7 @@
       <c r="B90" s="6">
         <v>45587</v>
       </c>
-      <c r="C90" s="33">
+      <c r="C90">
         <v>0</v>
       </c>
     </row>
@@ -4295,7 +4286,7 @@
       <c r="A91" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="33">
+      <c r="C91">
         <v>0</v>
       </c>
     </row>
@@ -4303,7 +4294,7 @@
       <c r="B92" s="6">
         <v>45188</v>
       </c>
-      <c r="C92" s="33">
+      <c r="C92">
         <v>0</v>
       </c>
     </row>
@@ -4311,7 +4302,7 @@
       <c r="A93" t="s">
         <v>5</v>
       </c>
-      <c r="C93" s="33">
+      <c r="C93">
         <v>0</v>
       </c>
     </row>
@@ -4319,7 +4310,7 @@
       <c r="B94" s="6">
         <v>45133</v>
       </c>
-      <c r="C94" s="33">
+      <c r="C94">
         <v>0</v>
       </c>
     </row>
@@ -4327,7 +4318,7 @@
       <c r="A95" t="s">
         <v>16</v>
       </c>
-      <c r="C95" s="33">
+      <c r="C95">
         <v>0</v>
       </c>
     </row>
@@ -4335,7 +4326,7 @@
       <c r="B96" s="6">
         <v>45954</v>
       </c>
-      <c r="C96" s="33">
+      <c r="C96">
         <v>0</v>
       </c>
     </row>
@@ -4343,7 +4334,7 @@
       <c r="A97" t="s">
         <v>20</v>
       </c>
-      <c r="C97" s="33">
+      <c r="C97">
         <v>0</v>
       </c>
     </row>
@@ -4351,7 +4342,7 @@
       <c r="B98" s="6">
         <v>45422</v>
       </c>
-      <c r="C98" s="33">
+      <c r="C98">
         <v>0</v>
       </c>
     </row>
@@ -4359,7 +4350,7 @@
       <c r="A99" t="s">
         <v>112</v>
       </c>
-      <c r="C99" s="33">
+      <c r="C99">
         <v>0</v>
       </c>
     </row>
@@ -4367,7 +4358,7 @@
       <c r="B100" s="6">
         <v>45223</v>
       </c>
-      <c r="C100" s="33">
+      <c r="C100">
         <v>0</v>
       </c>
     </row>
@@ -4401,10 +4392,10 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
@@ -4412,33 +4403,33 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="32">
         <v>44991</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="45">
+      <c r="C2" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="42">
         <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="32">
         <v>44993</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="45">
+      <c r="C3" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="42">
         <v>2000</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="30" t="s">
         <v>122</v>
       </c>
       <c r="G3" t="s">
@@ -4446,1502 +4437,1502 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="32">
         <v>44993</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="45">
+      <c r="C4" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="42">
         <v>1500</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="32">
         <v>44993</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="45">
+      <c r="C5" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="42">
         <v>1100</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="32">
         <v>45006</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="45">
+      <c r="C6" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="42">
         <v>1500</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <v>45006</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="45">
+      <c r="C7" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="42">
         <v>2000</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="32">
         <v>45029</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="45">
+      <c r="C8" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="32">
         <v>45029</v>
       </c>
-      <c r="C9" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="45">
+      <c r="C9" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="32">
         <v>45029</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="45">
+      <c r="C10" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="32">
         <v>45044</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>2200</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="32">
         <v>45044</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="42">
         <v>2400</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="32">
         <v>45100</v>
       </c>
-      <c r="C13" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="45">
+      <c r="C13" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="32">
         <v>45133</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="45">
+      <c r="C14" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="42">
         <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="32">
         <v>45133</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="45">
+      <c r="C15" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="42">
         <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="32">
         <v>45133</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="45">
+      <c r="C16" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="32">
         <v>45134</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="45">
+      <c r="C17" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="32">
         <v>45139</v>
       </c>
-      <c r="C18" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="45">
+      <c r="C18" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="32">
         <v>45175</v>
       </c>
-      <c r="C19" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="45">
+      <c r="C19" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="42">
         <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="32">
         <v>45175</v>
       </c>
-      <c r="C20" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="45">
+      <c r="C20" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="42">
         <v>800</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="32">
         <v>45177</v>
       </c>
-      <c r="C21" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="45">
+      <c r="C21" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="42">
         <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="32">
         <v>45188</v>
       </c>
-      <c r="C22" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="45">
+      <c r="C22" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="42">
         <v>800</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="32">
         <v>45188</v>
       </c>
-      <c r="C23" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="45">
+      <c r="C23" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="42">
         <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="32">
         <v>45188</v>
       </c>
-      <c r="C24" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="45">
+      <c r="C24" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="32">
         <v>45210</v>
       </c>
-      <c r="C25" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="45">
+      <c r="C25" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="32">
         <v>45223</v>
       </c>
-      <c r="C26" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="45">
+      <c r="C26" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="42">
         <v>700</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="32">
         <v>45223</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="45">
+      <c r="C27" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B28" s="32">
         <v>45223</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="45">
+      <c r="C28" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="32">
         <v>45270</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="45">
+      <c r="C29" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="42">
         <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="32">
         <v>45270</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="45">
+      <c r="C30" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="32">
         <v>45270</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="45">
+      <c r="C31" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="32">
         <v>45270</v>
       </c>
-      <c r="C32" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="45">
+      <c r="C32" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="32">
         <v>45270</v>
       </c>
-      <c r="C33" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="45">
+      <c r="C33" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="32">
         <v>45422</v>
       </c>
-      <c r="C34" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="45">
+      <c r="C34" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="42">
         <v>1200</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="A35" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="32">
         <v>45461</v>
       </c>
-      <c r="C35" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="45">
+      <c r="C35" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="32">
         <v>45464</v>
       </c>
-      <c r="C36" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="45">
+      <c r="C36" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="32">
         <v>45492</v>
       </c>
-      <c r="C37" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="45">
+      <c r="C37" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="32">
         <v>45492</v>
       </c>
-      <c r="C38" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="45">
+      <c r="C38" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="35">
+      <c r="B39" s="32">
         <v>45498</v>
       </c>
-      <c r="C39" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="45">
+      <c r="C39" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="42">
         <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="35">
+      <c r="B40" s="32">
         <v>45587</v>
       </c>
-      <c r="C40" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="45">
+      <c r="C40" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="42">
         <v>1100</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="35">
+      <c r="B41" s="32">
         <v>45630</v>
       </c>
-      <c r="C41" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="45">
+      <c r="C41" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="42">
         <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="32">
         <v>45680</v>
       </c>
-      <c r="C42" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="45">
+      <c r="C42" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="42">
         <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="34" t="s">
+      <c r="A43" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="32">
         <v>45680</v>
       </c>
-      <c r="C43" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" s="45">
+      <c r="C43" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="34" t="s">
+      <c r="A44" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="35">
+      <c r="B44" s="32">
         <v>45680</v>
       </c>
-      <c r="C44" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="45">
+      <c r="C44" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="42">
         <v>1100</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B45" s="35">
+      <c r="B45" s="32">
         <v>45714</v>
       </c>
-      <c r="C45" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="45">
+      <c r="C45" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="42">
         <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="35">
+      <c r="B46" s="32">
         <v>45714</v>
       </c>
-      <c r="C46" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="45">
+      <c r="C46" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="42">
         <v>900</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="35">
+      <c r="B47" s="32">
         <v>45714</v>
       </c>
-      <c r="C47" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" s="45">
+      <c r="C47" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+      <c r="A48" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="35">
+      <c r="B48" s="32">
         <v>45714</v>
       </c>
-      <c r="C48" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="45">
+      <c r="C48" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="42">
         <v>1100</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="34" t="s">
+      <c r="A49" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="B49" s="35">
+      <c r="B49" s="32">
         <v>45743</v>
       </c>
-      <c r="C49" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="45">
+      <c r="C49" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="B50" s="35">
+      <c r="B50" s="32">
         <v>45762</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="45">
+      <c r="D50" s="42">
         <v>2200</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="35">
+      <c r="B51" s="32">
         <v>45797</v>
       </c>
-      <c r="C51" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51" s="45">
+      <c r="C51" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="35">
+      <c r="B52" s="32">
         <v>45840</v>
       </c>
-      <c r="C52" s="36" t="s">
+      <c r="C52" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="45">
+      <c r="D52" s="42">
         <v>2000</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="B53" s="35">
+      <c r="B53" s="32">
         <v>45862</v>
       </c>
-      <c r="C53" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53" s="45">
+      <c r="C53" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="42">
         <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="B54" s="35">
+      <c r="B54" s="32">
         <v>45862</v>
       </c>
-      <c r="C54" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" s="45">
+      <c r="C54" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="42">
         <v>1100</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="34" t="s">
+      <c r="A55" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="35">
+      <c r="B55" s="32">
         <v>45870</v>
       </c>
-      <c r="C55" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="45">
+      <c r="C55" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="34" t="s">
+      <c r="A56" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="35">
+      <c r="B56" s="32">
         <v>45877</v>
       </c>
-      <c r="C56" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="45">
+      <c r="C56" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="42">
         <v>800</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="34" t="s">
+      <c r="A57" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="32">
         <v>45877</v>
       </c>
-      <c r="C57" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="45">
+      <c r="C57" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="42">
         <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="34" t="s">
+      <c r="A58" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="35">
+      <c r="B58" s="32">
         <v>45877</v>
       </c>
-      <c r="C58" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="45">
+      <c r="C58" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="34" t="s">
+      <c r="A59" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B59" s="35">
+      <c r="B59" s="32">
         <v>45877</v>
       </c>
-      <c r="C59" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="45">
+      <c r="C59" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" s="42">
         <v>1200</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="34" t="s">
+      <c r="A60" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="35">
+      <c r="B60" s="32">
         <v>45882</v>
       </c>
-      <c r="C60" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D60" s="45">
+      <c r="C60" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="34" t="s">
+      <c r="A61" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="B61" s="35">
+      <c r="B61" s="32">
         <v>45924</v>
       </c>
-      <c r="C61" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61" s="45">
+      <c r="C61" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="42">
         <v>700</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="34" t="s">
+      <c r="A62" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="B62" s="35">
+      <c r="B62" s="32">
         <v>45946</v>
       </c>
-      <c r="C62" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62" s="45">
+      <c r="C62" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="42">
         <v>700</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="34" t="s">
+      <c r="A63" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="B63" s="35">
+      <c r="B63" s="32">
         <v>45954</v>
       </c>
-      <c r="C63" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="45">
+      <c r="C63" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="34" t="s">
+      <c r="A64" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="B64" s="35">
+      <c r="B64" s="32">
         <v>45954</v>
       </c>
-      <c r="C64" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" s="45">
+      <c r="C64" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="34" t="s">
+      <c r="A65" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="35">
+      <c r="B65" s="32">
         <v>45958</v>
       </c>
-      <c r="C65" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="45">
+      <c r="C65" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="42">
         <v>2400</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="38" t="s">
+      <c r="A66" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="B66" s="39">
+      <c r="B66" s="36">
         <v>45958</v>
       </c>
-      <c r="C66" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" s="46">
+      <c r="C66" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="43">
         <v>2300</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="34" t="s">
+      <c r="A67" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="B67" s="35">
+      <c r="B67" s="32">
         <v>45966</v>
       </c>
-      <c r="C67" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D67" s="45">
+      <c r="C67" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="42">
         <v>2000</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="34" t="s">
+      <c r="A68" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B68" s="35">
+      <c r="B68" s="32">
         <v>45966</v>
       </c>
-      <c r="C68" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D68" s="45">
+      <c r="C68" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="42">
         <v>1000</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="34" t="s">
+      <c r="A69" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B69" s="35">
+      <c r="B69" s="32">
         <v>45966</v>
       </c>
-      <c r="C69" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="45">
+      <c r="C69" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="42">
         <v>1100</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="34" t="s">
+      <c r="A70" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B70" s="35">
+      <c r="B70" s="32">
         <v>45966</v>
       </c>
-      <c r="C70" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="45">
+      <c r="C70" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="42">
         <v>1800</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="34" t="s">
+      <c r="A71" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B71" s="35">
+      <c r="B71" s="32">
         <v>45971</v>
       </c>
-      <c r="C71" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" s="45">
+      <c r="C71" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="34" t="s">
+      <c r="A72" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="32">
         <v>45971</v>
       </c>
-      <c r="C72" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D72" s="45">
+      <c r="C72" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="34" t="s">
+      <c r="A73" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B73" s="35">
+      <c r="B73" s="32">
         <v>45973</v>
       </c>
-      <c r="C73" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="45">
+      <c r="C73" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" s="42">
         <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="34" t="s">
+      <c r="A74" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B74" s="35">
+      <c r="B74" s="32">
         <v>45973</v>
       </c>
-      <c r="C74" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D74" s="45">
+      <c r="C74" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="42">
         <v>1500</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="34" t="s">
+      <c r="A75" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="32">
         <v>45973</v>
       </c>
-      <c r="C75" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D75" s="45">
+      <c r="C75" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="42">
         <v>2000</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="34" t="s">
+      <c r="A76" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="B76" s="35">
+      <c r="B76" s="32">
         <v>45975</v>
       </c>
-      <c r="C76" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="45">
+      <c r="C76" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="42">
         <v>2100</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="34" t="s">
+      <c r="A77" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="35">
+      <c r="B77" s="32">
         <v>45975</v>
       </c>
-      <c r="C77" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D77" s="45">
+      <c r="C77" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" s="42">
         <v>2000</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="34" t="s">
+      <c r="A78" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="B78" s="35">
+      <c r="B78" s="32">
         <v>45981</v>
       </c>
-      <c r="C78" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="45">
+      <c r="C78" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="42">
         <v>1350</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="34" t="s">
+      <c r="A79" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B79" s="35">
+      <c r="B79" s="32">
         <v>45996</v>
       </c>
-      <c r="C79" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="45">
+      <c r="C79" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" s="42">
         <v>1200</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="38" t="s">
+      <c r="A80" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="39">
+      <c r="B80" s="36">
         <v>46041</v>
       </c>
-      <c r="C80" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" s="46">
+      <c r="C80" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" s="43">
         <v>1200</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="34" t="s">
+      <c r="A81" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="32">
         <v>46154</v>
       </c>
-      <c r="C81" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="46">
+      <c r="C81" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="43">
         <v>900</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="34" t="s">
+      <c r="A82" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B82" s="35">
+      <c r="B82" s="32">
         <v>46154</v>
       </c>
-      <c r="C82" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" s="45">
+      <c r="C82" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" s="42">
         <v>1650</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="35">
+      <c r="B83" s="32">
         <v>46164</v>
       </c>
-      <c r="C83" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" s="45">
+      <c r="C83" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" s="42">
         <v>2200</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="34"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="43"/>
+      <c r="A84" s="31"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="40"/>
     </row>
     <row r="85" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="34"/>
-      <c r="B85" s="35"/>
-      <c r="C85" s="47"/>
-      <c r="D85" s="43"/>
+      <c r="A85" s="31"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="40"/>
     </row>
     <row r="86" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="34"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="47"/>
-      <c r="D86" s="43"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="40"/>
     </row>
     <row r="87" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="34"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="43"/>
+      <c r="A87" s="31"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="40"/>
     </row>
     <row r="88" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="34"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="43"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="40"/>
     </row>
     <row r="89" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="34"/>
-      <c r="B89" s="35"/>
-      <c r="C89" s="47"/>
-      <c r="D89" s="43"/>
+      <c r="A89" s="31"/>
+      <c r="B89" s="32"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="40"/>
     </row>
     <row r="90" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="34"/>
-      <c r="B90" s="35"/>
-      <c r="C90" s="47"/>
-      <c r="D90" s="43"/>
+      <c r="A90" s="31"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="40"/>
     </row>
     <row r="91" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="34"/>
-      <c r="B91" s="35"/>
-      <c r="C91" s="47"/>
-      <c r="D91" s="43"/>
+      <c r="A91" s="31"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="40"/>
     </row>
     <row r="92" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="34"/>
-      <c r="B92" s="35"/>
-      <c r="C92" s="47"/>
-      <c r="D92" s="43"/>
+      <c r="A92" s="31"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="40"/>
     </row>
     <row r="93" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="34"/>
-      <c r="B93" s="35"/>
-      <c r="C93" s="47"/>
-      <c r="D93" s="43"/>
+      <c r="A93" s="31"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="40"/>
     </row>
     <row r="94" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="34"/>
-      <c r="B94" s="35"/>
-      <c r="C94" s="47"/>
-      <c r="D94" s="43"/>
+      <c r="A94" s="31"/>
+      <c r="B94" s="32"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="40"/>
     </row>
     <row r="95" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="34"/>
-      <c r="B95" s="35"/>
-      <c r="C95" s="47"/>
-      <c r="D95" s="43"/>
+      <c r="A95" s="31"/>
+      <c r="B95" s="32"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="40"/>
     </row>
     <row r="96" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="34"/>
-      <c r="B96" s="35"/>
-      <c r="C96" s="47"/>
-      <c r="D96" s="43"/>
+      <c r="A96" s="31"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="40"/>
     </row>
     <row r="97" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="34"/>
-      <c r="B97" s="35"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="43"/>
+      <c r="A97" s="31"/>
+      <c r="B97" s="32"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="40"/>
     </row>
     <row r="98" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="34"/>
-      <c r="B98" s="35"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="43"/>
+      <c r="A98" s="31"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="40"/>
     </row>
     <row r="99" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="34"/>
-      <c r="B99" s="35"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="43"/>
+      <c r="A99" s="31"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="40"/>
     </row>
     <row r="100" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="34"/>
-      <c r="B100" s="35"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="43"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="40"/>
     </row>
     <row r="101" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="34"/>
-      <c r="B101" s="35"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="43"/>
+      <c r="A101" s="31"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="40"/>
     </row>
     <row r="102" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="34"/>
-      <c r="B102" s="35"/>
-      <c r="C102" s="47"/>
-      <c r="D102" s="43"/>
+      <c r="A102" s="31"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="40"/>
     </row>
     <row r="103" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="34"/>
-      <c r="B103" s="35"/>
-      <c r="C103" s="47"/>
-      <c r="D103" s="43"/>
+      <c r="A103" s="31"/>
+      <c r="B103" s="32"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="40"/>
     </row>
     <row r="104" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="34"/>
-      <c r="B104" s="35"/>
-      <c r="C104" s="47"/>
-      <c r="D104" s="43"/>
+      <c r="A104" s="31"/>
+      <c r="B104" s="32"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="40"/>
     </row>
     <row r="105" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="34"/>
-      <c r="B105" s="35"/>
-      <c r="C105" s="47"/>
-      <c r="D105" s="43"/>
+      <c r="A105" s="31"/>
+      <c r="B105" s="32"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="40"/>
     </row>
     <row r="106" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="34"/>
-      <c r="B106" s="35"/>
-      <c r="C106" s="47"/>
-      <c r="D106" s="43"/>
+      <c r="A106" s="31"/>
+      <c r="B106" s="32"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="40"/>
     </row>
     <row r="107" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="34"/>
-      <c r="B107" s="35"/>
-      <c r="C107" s="47"/>
-      <c r="D107" s="43"/>
+      <c r="A107" s="31"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="40"/>
     </row>
     <row r="108" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="34"/>
-      <c r="B108" s="35"/>
-      <c r="C108" s="47"/>
-      <c r="D108" s="43"/>
+      <c r="A108" s="31"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="44"/>
+      <c r="D108" s="40"/>
     </row>
     <row r="109" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="34"/>
-      <c r="B109" s="35"/>
-      <c r="C109" s="47"/>
-      <c r="D109" s="43"/>
+      <c r="A109" s="31"/>
+      <c r="B109" s="32"/>
+      <c r="C109" s="44"/>
+      <c r="D109" s="40"/>
     </row>
     <row r="110" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="34"/>
-      <c r="B110" s="35"/>
-      <c r="C110" s="47"/>
-      <c r="D110" s="43"/>
+      <c r="A110" s="31"/>
+      <c r="B110" s="32"/>
+      <c r="C110" s="44"/>
+      <c r="D110" s="40"/>
     </row>
     <row r="111" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="34"/>
-      <c r="B111" s="35"/>
-      <c r="C111" s="47"/>
-      <c r="D111" s="43"/>
+      <c r="A111" s="31"/>
+      <c r="B111" s="32"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="40"/>
     </row>
     <row r="112" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="34"/>
-      <c r="B112" s="35"/>
-      <c r="C112" s="47"/>
-      <c r="D112" s="43"/>
+      <c r="A112" s="31"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="40"/>
     </row>
     <row r="113" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="34"/>
-      <c r="B113" s="35"/>
-      <c r="C113" s="47"/>
-      <c r="D113" s="43"/>
+      <c r="A113" s="31"/>
+      <c r="B113" s="32"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="40"/>
     </row>
     <row r="114" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="34"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="47"/>
-      <c r="D114" s="43"/>
+      <c r="A114" s="31"/>
+      <c r="B114" s="32"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="40"/>
     </row>
     <row r="115" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="34"/>
-      <c r="B115" s="35"/>
-      <c r="C115" s="47"/>
-      <c r="D115" s="43"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="32"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="40"/>
     </row>
     <row r="116" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="34"/>
-      <c r="B116" s="35"/>
-      <c r="C116" s="47"/>
-      <c r="D116" s="43"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="32"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="40"/>
     </row>
     <row r="117" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="34"/>
-      <c r="B117" s="35"/>
-      <c r="C117" s="47"/>
-      <c r="D117" s="43"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="32"/>
+      <c r="C117" s="44"/>
+      <c r="D117" s="40"/>
     </row>
     <row r="118" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="34"/>
-      <c r="B118" s="35"/>
-      <c r="C118" s="47"/>
-      <c r="D118" s="43"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="32"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="40"/>
     </row>
     <row r="119" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="34"/>
-      <c r="B119" s="35"/>
-      <c r="C119" s="47"/>
-      <c r="D119" s="43"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="32"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="40"/>
     </row>
     <row r="120" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="34"/>
-      <c r="B120" s="35"/>
-      <c r="C120" s="47"/>
-      <c r="D120" s="43"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="32"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="40"/>
     </row>
     <row r="121" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="34"/>
-      <c r="B121" s="35"/>
-      <c r="C121" s="47"/>
-      <c r="D121" s="43"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="32"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="40"/>
     </row>
     <row r="122" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="34"/>
-      <c r="B122" s="35"/>
-      <c r="C122" s="47"/>
-      <c r="D122" s="43"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="32"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="40"/>
     </row>
     <row r="123" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="34"/>
-      <c r="B123" s="35"/>
-      <c r="C123" s="47"/>
-      <c r="D123" s="43"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="32"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="40"/>
     </row>
     <row r="124" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="34"/>
-      <c r="B124" s="35"/>
-      <c r="C124" s="47"/>
-      <c r="D124" s="43"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="32"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="40"/>
     </row>
     <row r="125" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="34"/>
-      <c r="B125" s="35"/>
-      <c r="C125" s="47"/>
-      <c r="D125" s="43"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="32"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="40"/>
     </row>
     <row r="126" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="34"/>
-      <c r="B126" s="35"/>
-      <c r="C126" s="47"/>
-      <c r="D126" s="43"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="32"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="40"/>
     </row>
     <row r="127" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="34"/>
-      <c r="B127" s="35"/>
-      <c r="C127" s="47"/>
-      <c r="D127" s="43"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="32"/>
+      <c r="C127" s="44"/>
+      <c r="D127" s="40"/>
     </row>
     <row r="128" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="34"/>
-      <c r="B128" s="35"/>
-      <c r="C128" s="47"/>
-      <c r="D128" s="43"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="32"/>
+      <c r="C128" s="44"/>
+      <c r="D128" s="40"/>
     </row>
     <row r="129" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="34"/>
-      <c r="B129" s="35"/>
-      <c r="C129" s="47"/>
-      <c r="D129" s="43"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="32"/>
+      <c r="C129" s="44"/>
+      <c r="D129" s="40"/>
     </row>
     <row r="130" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="34"/>
-      <c r="B130" s="35"/>
-      <c r="C130" s="47"/>
-      <c r="D130" s="43"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="32"/>
+      <c r="C130" s="44"/>
+      <c r="D130" s="40"/>
     </row>
     <row r="131" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="34"/>
-      <c r="B131" s="35"/>
-      <c r="C131" s="47"/>
-      <c r="D131" s="43"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="32"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="40"/>
     </row>
     <row r="132" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="34"/>
-      <c r="B132" s="35"/>
-      <c r="C132" s="47"/>
-      <c r="D132" s="43"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="32"/>
+      <c r="C132" s="44"/>
+      <c r="D132" s="40"/>
     </row>
     <row r="133" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="34"/>
-      <c r="B133" s="35"/>
-      <c r="C133" s="47"/>
-      <c r="D133" s="43"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="32"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="40"/>
     </row>
     <row r="134" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="34"/>
-      <c r="B134" s="35"/>
-      <c r="C134" s="47"/>
-      <c r="D134" s="43"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="32"/>
+      <c r="C134" s="44"/>
+      <c r="D134" s="40"/>
     </row>
     <row r="135" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="34"/>
-      <c r="B135" s="35"/>
-      <c r="C135" s="47"/>
-      <c r="D135" s="43"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="32"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="40"/>
     </row>
     <row r="136" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="34"/>
-      <c r="B136" s="35"/>
-      <c r="C136" s="47"/>
-      <c r="D136" s="43"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="32"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="40"/>
     </row>
     <row r="137" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="34"/>
-      <c r="B137" s="35"/>
-      <c r="C137" s="47"/>
-      <c r="D137" s="43"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="32"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="40"/>
     </row>
     <row r="138" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="34"/>
-      <c r="B138" s="35"/>
-      <c r="C138" s="47"/>
-      <c r="D138" s="43"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="32"/>
+      <c r="C138" s="44"/>
+      <c r="D138" s="40"/>
     </row>
     <row r="139" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="34"/>
-      <c r="B139" s="35"/>
-      <c r="C139" s="47"/>
-      <c r="D139" s="43"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="32"/>
+      <c r="C139" s="44"/>
+      <c r="D139" s="40"/>
     </row>
     <row r="140" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="34"/>
-      <c r="B140" s="35"/>
-      <c r="C140" s="47"/>
-      <c r="D140" s="43"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="32"/>
+      <c r="C140" s="44"/>
+      <c r="D140" s="40"/>
     </row>
     <row r="141" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="34"/>
-      <c r="B141" s="35"/>
-      <c r="C141" s="47"/>
-      <c r="D141" s="43"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="32"/>
+      <c r="C141" s="44"/>
+      <c r="D141" s="40"/>
     </row>
     <row r="142" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="34"/>
-      <c r="B142" s="35"/>
-      <c r="C142" s="47"/>
-      <c r="D142" s="43"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="32"/>
+      <c r="C142" s="44"/>
+      <c r="D142" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5957,13 +5948,12 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="24"/>
-    <col min="2" max="2" width="69.25" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="25"/>
-    <col min="4" max="4" width="11.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="9" style="23"/>
+    <col min="2" max="2" width="69.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="24"/>
+    <col min="4" max="4" width="11.125" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.25" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5987,302 +5977,302 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>2200</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>2</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="15">
         <v>46112</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="27" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>1800</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="14">
         <v>2</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <v>45284</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="27" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>800</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="14">
         <v>2</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>45598</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1500</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="14">
         <v>2</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>45628</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>400</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>1</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>45628</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>1650</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <v>6</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>45761</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <v>500</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>2</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>46022</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="27" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>800</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>4</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>45832</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+      <c r="A10" s="12">
         <v>1100</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>2</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>45730</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+      <c r="A11" s="12">
         <v>900</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>1</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>45730</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <v>1800</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>2</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>46197</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <v>1500</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <v>2</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>46197</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <v>1350</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>46197</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <v>1000</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>46197</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <v>700</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>1</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>46197</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="28" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6306,7 +6296,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="30" t="s">
         <v>122</v>
       </c>
       <c r="B3" t="s">
@@ -6320,7 +6310,7 @@
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4">
         <v>500</v>
       </c>
       <c r="C4" s="4">
@@ -6331,7 +6321,7 @@
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5">
         <v>800</v>
       </c>
       <c r="C5" s="4">
@@ -6342,7 +6332,7 @@
       <c r="A6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6">
         <v>2200</v>
       </c>
       <c r="C6" s="4">
@@ -6353,7 +6343,7 @@
       <c r="A7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7">
         <v>1650</v>
       </c>
       <c r="C7" s="4">
@@ -6364,7 +6354,7 @@
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8">
         <v>800</v>
       </c>
       <c r="C8" s="4">
@@ -6375,7 +6365,7 @@
       <c r="A9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9">
         <v>1800</v>
       </c>
       <c r="C9" s="4">
@@ -6386,7 +6376,7 @@
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10">
         <v>1100</v>
       </c>
       <c r="C10" s="4">
@@ -6397,7 +6387,7 @@
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11">
         <v>1800</v>
       </c>
       <c r="C11" s="4">
@@ -6408,7 +6398,7 @@
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12">
         <v>1500</v>
       </c>
       <c r="C12" s="4">
@@ -6419,7 +6409,7 @@
       <c r="A13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13">
         <v>2200</v>
       </c>
       <c r="C13" s="4">
